--- a/artfynd/A 61151-2025 artfynd.xlsx
+++ b/artfynd/A 61151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74499908</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97534</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>45 Vemmesån, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>469803</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6359092</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vrigstad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1987-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1993-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E2e 1613. SOM: Huperzia selago. LEG: Eira Petersson, Thomas Karlsson, Sonja Gustafsson, Dag Ekholm</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Berg i skog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 61151-2025 artfynd.xlsx
+++ b/artfynd/A 61151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74129369</v>
+        <v>102015087</v>
       </c>
       <c r="B2" t="n">
-        <v>98573</v>
+        <v>107908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>219955</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>45 Vemmesån, Sm</t>
+          <t>Köpstad norr om, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469803</v>
+        <v>470113</v>
       </c>
       <c r="R2" t="n">
-        <v>6359092</v>
+        <v>6359873</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -738,19 +750,24 @@
           <t>Vrigstad</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>F-Säv-0237</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1987-01-01</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1993-12-31</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6E2e 1613. SOM: Corallorhiza trifida. LEG: Eira Petersson, Thomas Karlsson, Sonja Gustafsson, Dag Ekholm</t>
+          <t>Rosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,14 +776,10 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kärr vid å</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -775,21 +788,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Smålands flora (1978-2007)</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74499908</v>
+        <v>74129369</v>
       </c>
       <c r="B3" t="n">
-        <v>97534</v>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,19 +810,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -857,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6E2e 1613. SOM: Huperzia selago. LEG: Eira Petersson, Thomas Karlsson, Sonja Gustafsson, Dag Ekholm</t>
+          <t>Smålands flora 2007: KOO: 6E2e 1613. SOM: Corallorhiza trifida. LEG: Eira Petersson, Thomas Karlsson, Sonja Gustafsson, Dag Ekholm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +888,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Berg i skog</t>
+          <t>Kärr vid å</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -886,6 +903,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>74499908</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>45 Vemmesån, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>469803</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6359092</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vrigstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1987-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1993-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E2e 1613. SOM: Huperzia selago. LEG: Eira Petersson, Thomas Karlsson, Sonja Gustafsson, Dag Ekholm</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Berg i skog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 61151-2025 artfynd.xlsx
+++ b/artfynd/A 61151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102015087</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74129369</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,8 +1029,18 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74499908</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>